--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3532B31D-BE34-49E0-8D12-07E4EE3E099D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A258C46B-02BF-4D10-AA3C-89F044671C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -304,9 +304,6 @@
     <t>#05 BEBIDA - CERVEJAS</t>
   </si>
   <si>
-    <t>CERVEJA ANTARCTICA SUBZERO 269ML</t>
-  </si>
-  <si>
     <t xml:space="preserve">CERVEJA HEINEKEN LAGER LONG NECK 250ML </t>
   </si>
   <si>
@@ -329,6 +326,9 @@
   </si>
   <si>
     <t>WHISKY OLD PARR 1L 12 ANOS</t>
+  </si>
+  <si>
+    <t>CERVEJA ANTARCTICA SUBZERO 15 X 269ML</t>
   </si>
 </sst>
 </file>
@@ -416,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -430,14 +430,8 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -755,8 +749,8 @@
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="49.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -772,10 +766,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -792,8 +786,8 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="9">
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
         <v>20.99</v>
       </c>
     </row>
@@ -810,8 +804,8 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="9">
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
         <v>15.99</v>
       </c>
     </row>
@@ -828,8 +822,8 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="9">
+      <c r="E4" s="5"/>
+      <c r="F4" s="7">
         <v>15.99</v>
       </c>
     </row>
@@ -846,8 +840,8 @@
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="9">
+      <c r="E5" s="5"/>
+      <c r="F5" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -864,8 +858,8 @@
       <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="9">
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
         <v>6.19</v>
       </c>
     </row>
@@ -882,8 +876,8 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="9">
+      <c r="E7" s="5"/>
+      <c r="F7" s="7">
         <v>6.19</v>
       </c>
     </row>
@@ -900,8 +894,8 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="9">
+      <c r="E8" s="5"/>
+      <c r="F8" s="7">
         <v>8.99</v>
       </c>
     </row>
@@ -918,8 +912,8 @@
       <c r="D9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="9">
+      <c r="E9" s="5"/>
+      <c r="F9" s="7">
         <v>34.99</v>
       </c>
     </row>
@@ -936,8 +930,8 @@
       <c r="D11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="9">
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
         <v>11.99</v>
       </c>
     </row>
@@ -954,8 +948,8 @@
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="9">
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
         <v>7.19</v>
       </c>
     </row>
@@ -972,8 +966,8 @@
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="9">
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
         <v>17.100000000000001</v>
       </c>
     </row>
@@ -990,8 +984,8 @@
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="9">
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
         <v>16.2</v>
       </c>
     </row>
@@ -1008,8 +1002,8 @@
       <c r="D15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="9">
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
         <v>16.2</v>
       </c>
     </row>
@@ -1026,8 +1020,8 @@
       <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="9">
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
         <v>7.2</v>
       </c>
     </row>
@@ -1044,8 +1038,8 @@
       <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="9">
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
         <v>6.99</v>
       </c>
     </row>
@@ -1062,8 +1056,8 @@
       <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="9">
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
         <v>7.59</v>
       </c>
     </row>
@@ -1080,8 +1074,8 @@
       <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="9">
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
         <v>8.1</v>
       </c>
     </row>
@@ -1098,8 +1092,8 @@
       <c r="D20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="9">
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
         <v>24.99</v>
       </c>
     </row>
@@ -1116,8 +1110,8 @@
       <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="9">
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
         <v>7.99</v>
       </c>
     </row>
@@ -1134,8 +1128,8 @@
       <c r="D22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="9">
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
         <v>7.49</v>
       </c>
     </row>
@@ -1152,8 +1146,8 @@
       <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="9">
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
         <v>14.49</v>
       </c>
     </row>
@@ -1170,8 +1164,8 @@
       <c r="D24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="9">
+      <c r="E24" s="5"/>
+      <c r="F24" s="7">
         <v>2.19</v>
       </c>
     </row>
@@ -1188,8 +1182,8 @@
       <c r="D25" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E25" s="6"/>
-      <c r="F25" s="9">
+      <c r="E25" s="5"/>
+      <c r="F25" s="7">
         <v>14.49</v>
       </c>
     </row>
@@ -1206,8 +1200,8 @@
       <c r="D26" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E26" s="6"/>
-      <c r="F26" s="9">
+      <c r="E26" s="5"/>
+      <c r="F26" s="7">
         <v>3.79</v>
       </c>
     </row>
@@ -1224,8 +1218,8 @@
       <c r="D27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="6"/>
-      <c r="F27" s="9">
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
         <v>3.99</v>
       </c>
     </row>
@@ -1242,8 +1236,8 @@
       <c r="D28" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="6"/>
-      <c r="F28" s="9">
+      <c r="E28" s="5"/>
+      <c r="F28" s="7">
         <v>27.99</v>
       </c>
     </row>
@@ -1260,8 +1254,8 @@
       <c r="D29" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="9">
+      <c r="E29" s="5"/>
+      <c r="F29" s="7">
         <v>2.89</v>
       </c>
     </row>
@@ -1278,8 +1272,8 @@
       <c r="D30" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="6"/>
-      <c r="F30" s="9">
+      <c r="E30" s="5"/>
+      <c r="F30" s="7">
         <v>8.49</v>
       </c>
     </row>
@@ -1296,10 +1290,10 @@
       <c r="D31" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="7">
         <v>5.59</v>
       </c>
     </row>
@@ -1316,8 +1310,8 @@
       <c r="D32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="9">
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
         <v>7.99</v>
       </c>
     </row>
@@ -1334,8 +1328,8 @@
       <c r="D33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="9">
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
         <v>23.99</v>
       </c>
     </row>
@@ -1352,8 +1346,8 @@
       <c r="D34" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="9">
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
         <v>2.59</v>
       </c>
     </row>
@@ -1370,8 +1364,8 @@
       <c r="D35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="9">
+      <c r="E35" s="5"/>
+      <c r="F35" s="7">
         <v>3.39</v>
       </c>
     </row>
@@ -1388,8 +1382,8 @@
       <c r="D36" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="9">
+      <c r="E36" s="5"/>
+      <c r="F36" s="7">
         <v>8.49</v>
       </c>
     </row>
@@ -1406,8 +1400,8 @@
       <c r="D37" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="6"/>
-      <c r="F37" s="9">
+      <c r="E37" s="5"/>
+      <c r="F37" s="7">
         <v>5.99</v>
       </c>
     </row>
@@ -1424,8 +1418,8 @@
       <c r="D38" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E38" s="6"/>
-      <c r="F38" s="9">
+      <c r="E38" s="5"/>
+      <c r="F38" s="7">
         <v>10.99</v>
       </c>
     </row>
@@ -1442,8 +1436,8 @@
       <c r="D39" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="6"/>
-      <c r="F39" s="9">
+      <c r="E39" s="5"/>
+      <c r="F39" s="7">
         <v>3.39</v>
       </c>
     </row>
@@ -1460,8 +1454,8 @@
       <c r="D40" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="9">
+      <c r="E40" s="5"/>
+      <c r="F40" s="7">
         <v>7.19</v>
       </c>
     </row>
@@ -1478,8 +1472,8 @@
       <c r="D41" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E41" s="6"/>
-      <c r="F41" s="9">
+      <c r="E41" s="5"/>
+      <c r="F41" s="7">
         <v>39.99</v>
       </c>
     </row>
@@ -1496,8 +1490,8 @@
       <c r="D42" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="9">
+      <c r="E42" s="5"/>
+      <c r="F42" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -1514,8 +1508,8 @@
       <c r="D43" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="6"/>
-      <c r="F43" s="9">
+      <c r="E43" s="5"/>
+      <c r="F43" s="7">
         <v>3.19</v>
       </c>
     </row>
@@ -1532,8 +1526,8 @@
       <c r="D44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="6"/>
-      <c r="F44" s="9">
+      <c r="E44" s="5"/>
+      <c r="F44" s="7">
         <v>2.99</v>
       </c>
     </row>
@@ -1550,8 +1544,8 @@
       <c r="D45" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E45" s="6"/>
-      <c r="F45" s="9">
+      <c r="E45" s="5"/>
+      <c r="F45" s="7">
         <v>2.69</v>
       </c>
     </row>
@@ -1568,8 +1562,8 @@
       <c r="D46" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="6"/>
-      <c r="F46" s="9">
+      <c r="E46" s="5"/>
+      <c r="F46" s="7">
         <v>2.69</v>
       </c>
     </row>
@@ -1586,8 +1580,8 @@
       <c r="D48" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="9">
+      <c r="E48" s="5"/>
+      <c r="F48" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
@@ -1604,8 +1598,8 @@
       <c r="D49" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="9">
+      <c r="E49" s="5"/>
+      <c r="F49" s="7">
         <v>4.59</v>
       </c>
     </row>
@@ -1622,8 +1616,8 @@
       <c r="D50" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="9">
+      <c r="E50" s="5"/>
+      <c r="F50" s="7">
         <v>33.99</v>
       </c>
     </row>
@@ -1640,8 +1634,8 @@
       <c r="D51" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="9">
+      <c r="E51" s="5"/>
+      <c r="F51" s="7">
         <v>11.99</v>
       </c>
     </row>
@@ -1658,10 +1652,10 @@
       <c r="D52" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="7">
         <v>13.99</v>
       </c>
     </row>
@@ -1678,10 +1672,10 @@
       <c r="D53" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="7">
         <v>11.49</v>
       </c>
     </row>
@@ -1698,8 +1692,8 @@
       <c r="D54" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="6"/>
-      <c r="F54" s="9">
+      <c r="E54" s="5"/>
+      <c r="F54" s="7">
         <v>6.49</v>
       </c>
     </row>
@@ -1716,8 +1710,8 @@
       <c r="D55" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E55" s="6"/>
-      <c r="F55" s="9">
+      <c r="E55" s="5"/>
+      <c r="F55" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -1734,10 +1728,10 @@
       <c r="D56" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="7">
         <v>5.59</v>
       </c>
     </row>
@@ -1754,8 +1748,8 @@
       <c r="D58" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="6"/>
-      <c r="F58" s="9">
+      <c r="E58" s="5"/>
+      <c r="F58" s="7">
         <v>21.99</v>
       </c>
     </row>
@@ -1772,8 +1766,8 @@
       <c r="D60" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="9">
+      <c r="E60" s="5"/>
+      <c r="F60" s="7">
         <v>10.49</v>
       </c>
     </row>
@@ -1790,8 +1784,8 @@
       <c r="D61" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E61" s="6"/>
-      <c r="F61" s="9">
+      <c r="E61" s="5"/>
+      <c r="F61" s="7">
         <v>9.49</v>
       </c>
     </row>
@@ -1808,8 +1802,8 @@
       <c r="D62" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E62" s="6"/>
-      <c r="F62" s="9">
+      <c r="E62" s="5"/>
+      <c r="F62" s="7">
         <v>9.49</v>
       </c>
     </row>
@@ -1826,8 +1820,8 @@
       <c r="D63" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E63" s="6"/>
-      <c r="F63" s="9">
+      <c r="E63" s="5"/>
+      <c r="F63" s="7">
         <v>4.99</v>
       </c>
     </row>
@@ -1844,8 +1838,8 @@
       <c r="D64" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E64" s="6"/>
-      <c r="F64" s="9">
+      <c r="E64" s="5"/>
+      <c r="F64" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
@@ -1862,8 +1856,8 @@
       <c r="D65" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E65" s="6"/>
-      <c r="F65" s="9">
+      <c r="E65" s="5"/>
+      <c r="F65" s="7">
         <v>5.99</v>
       </c>
     </row>
@@ -1878,11 +1872,12 @@
         <v>239441</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E66" s="6"/>
-      <c r="F66" s="9">
-        <v>3.05</v>
+        <v>102</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="7">
+        <f>15*3.05</f>
+        <v>45.75</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1896,10 +1891,10 @@
         <v>184034</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="6"/>
-      <c r="F67" s="9">
+        <v>94</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="7">
         <v>5.49</v>
       </c>
     </row>
@@ -1914,10 +1909,10 @@
         <v>244191</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="9">
+        <v>95</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="7">
         <v>6.69</v>
       </c>
     </row>
@@ -1926,17 +1921,18 @@
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C69" s="3">
         <v>298701</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="9">
-        <v>3.99</v>
+        <v>97</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="7">
+        <f>12*3.99</f>
+        <v>47.88</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -1944,17 +1940,18 @@
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C70" s="3">
         <v>324556</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="9">
-        <v>2.89</v>
+        <v>98</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="7">
+        <f>15*2.89</f>
+        <v>43.35</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -1962,16 +1959,16 @@
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C71" s="3">
         <v>102085</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="9">
+        <v>100</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="7">
         <v>13.5</v>
       </c>
     </row>
@@ -1980,16 +1977,16 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C72" s="3">
         <v>102077</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="9">
+        <v>101</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="7">
         <v>179.99</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDD9A5E-D007-4D2A-A636-2E66EBB0662A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3524CA-D35C-4356-8109-7059A59431B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,9 +313,6 @@
     <t>#05 BEBIDA - CERVEJAS</t>
   </si>
   <si>
-    <t>CERVEJA ANTARCTICA SUBZERO 269ML</t>
-  </si>
-  <si>
     <t>CERVEJA SPATEN PURO MALTE LONG NECK 355ML</t>
   </si>
   <si>
@@ -335,6 +332,9 @@
   </si>
   <si>
     <t>LAVA ROUPAS TUFF CONCENTRADO 1L</t>
+  </si>
+  <si>
+    <t>CERVEJA ANTARCTICA SUBZERO 15 X 269ML</t>
   </si>
 </sst>
 </file>
@@ -1570,7 +1570,7 @@
         <v>115574</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="7">
@@ -1894,11 +1894,12 @@
         <v>239441</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="7">
-        <v>2.99</v>
+        <f>15*2.99</f>
+        <v>44.85</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1912,7 +1913,7 @@
         <v>259118</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E67" s="5"/>
       <c r="F67" s="7">
@@ -1924,13 +1925,13 @@
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C68" s="3">
         <v>287369</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="7">
@@ -1943,13 +1944,13 @@
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C69" s="3">
         <v>324556</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E69" s="5"/>
       <c r="F69" s="7">
@@ -1962,13 +1963,13 @@
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C70" s="3">
         <v>102242</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E70" s="5"/>
       <c r="F70" s="7">

--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1265327C-B4A5-44AC-92D9-2D3827282DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC49A72-0AAA-4DFA-8F63-FF71DDA2D6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -341,7 +341,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -361,21 +361,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -419,7 +429,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -427,28 +437,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -755,1236 +769,1236 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F71"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="42.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="101" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>335057</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>100020</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>301961</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>342706</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="9">
         <v>6.89</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>163918</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9">
         <v>9.39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>140665</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>106680</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="8"/>
       <c r="F8" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>255232</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>101137</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>101136</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>261728</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>270193</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>286197</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="9">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>338763</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>273714</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>188242</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>287073</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="6"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="9">
         <v>2.19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>100876</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="9">
         <v>16.690000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>111514</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="9">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>234316</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="9">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>170085</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="9">
         <v>25.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>106854</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="8" t="s">
         <v>38</v>
       </c>
       <c r="F24" s="9">
         <v>11.59</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>112978</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>109159</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="6"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="9">
         <v>7.69</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>100030</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>107361</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="6"/>
+      <c r="E28" s="8"/>
       <c r="F28" s="9">
         <v>5.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>273006</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="6"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>100119</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="6"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="9">
         <v>2.69</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>138206</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="6"/>
+      <c r="E31" s="8"/>
       <c r="F31" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>313827</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="6"/>
+      <c r="E32" s="8"/>
       <c r="F32" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>266749</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="6"/>
+      <c r="E33" s="8"/>
       <c r="F33" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>101066</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="6"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="9">
         <v>3.09</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>101083</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="6"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="9">
         <v>7.09</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>142446</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E36" s="6"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>108252</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E37" s="6"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>106922</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="6"/>
+      <c r="E38" s="8"/>
       <c r="F38" s="9">
         <v>36.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="6">
         <v>303196</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="6"/>
+      <c r="E39" s="8"/>
       <c r="F39" s="9">
         <v>3.39</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="6">
         <v>328759</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="6"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="6">
         <v>126425</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="6"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="9">
         <v>3.19</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="6">
         <v>209415</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E42" s="6"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="6">
         <v>207638</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="6"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="9">
         <v>3.19</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="6">
         <v>100431</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="6"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="9">
         <v>8.1</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="6">
         <v>100568</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="6"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="9">
         <v>13.5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="6">
         <v>286281</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="6"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="9">
         <v>12.6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="6">
         <v>142863</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="8" t="s">
         <v>70</v>
       </c>
       <c r="F48" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="6">
         <v>106663</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="6"/>
+      <c r="E49" s="8"/>
       <c r="F49" s="9">
         <v>2.69</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="6">
         <v>326954</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="6">
         <v>261980</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E51" s="6"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="6">
         <v>286199</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="8" t="s">
         <v>77</v>
       </c>
       <c r="F52" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="6">
         <v>100373</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E53" s="6"/>
+      <c r="E53" s="8"/>
       <c r="F53" s="9">
         <v>25.59</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="6">
         <v>219705</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="6"/>
+      <c r="E55" s="8"/>
       <c r="F55" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="6">
         <v>161871</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E57" s="6"/>
+      <c r="E57" s="8"/>
       <c r="F57" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="6">
         <v>104406</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E58" s="6"/>
+      <c r="E58" s="8"/>
       <c r="F58" s="9">
         <v>10.49</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="6">
         <v>104403</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E59" s="6"/>
+      <c r="E59" s="8"/>
       <c r="F59" s="9">
         <v>9.49</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="6">
         <v>286271</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E60" s="6"/>
+      <c r="E60" s="8"/>
       <c r="F60" s="9">
         <v>7.19</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="6">
         <v>102282</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E61" s="6"/>
+      <c r="E61" s="8"/>
       <c r="F61" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="6">
         <v>264452</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E62" s="6"/>
+      <c r="E62" s="8"/>
       <c r="F62" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="6">
         <v>220499</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E63" s="6"/>
+      <c r="E63" s="8"/>
       <c r="F63" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="6">
         <v>239446</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E64" s="6"/>
+      <c r="E64" s="8"/>
       <c r="F64" s="9">
         <f>12*3.39</f>
         <v>40.68</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="6">
         <v>170657</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E65" s="6"/>
+      <c r="E65" s="8"/>
       <c r="F65" s="9">
         <f>15*3.29</f>
         <v>49.35</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="6">
         <v>324556</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E66" s="6"/>
+      <c r="E66" s="8"/>
       <c r="F66" s="9">
         <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="6">
         <v>102242</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E67" s="6"/>
+      <c r="E67" s="8"/>
       <c r="F67" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="6">
         <v>102075</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="E68" s="6"/>
+      <c r="E68" s="8"/>
       <c r="F68" s="9">
         <v>135.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="6">
         <v>102077</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E69" s="6"/>
+      <c r="E69" s="8"/>
       <c r="F69" s="9">
         <v>179.99</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="6">
         <v>295198</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E70" s="6"/>
+      <c r="E70" s="8"/>
       <c r="F70" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="6">
         <v>102036</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E71" s="6"/>
+      <c r="E71" s="8"/>
       <c r="F71" s="9">
         <v>24.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AF1C3F-8C6F-46D7-B35D-CBD0141730A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A88C0AC-0517-40B5-B331-C506B2AA97F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="11010" windowHeight="12885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -278,7 +278,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,51 +291,34 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -385,46 +368,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -731,865 +705,866 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="39.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="68.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.28515625" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>100020</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9">
+      <c r="E2" s="6"/>
+      <c r="F2" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>100031</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9">
+      <c r="E3" s="6"/>
+      <c r="F3" s="7">
         <v>25.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>342706</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9">
+      <c r="E4" s="6"/>
+      <c r="F4" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>279573</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9">
+      <c r="E5" s="6"/>
+      <c r="F5" s="7">
         <v>9.19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="9">
         <v>167128</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12">
+      <c r="E6" s="8"/>
+      <c r="F6" s="10">
         <v>7.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>255232</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="9">
+      <c r="E8" s="6"/>
+      <c r="F8" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>101137</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="9">
+      <c r="E9" s="6"/>
+      <c r="F9" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>261728</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="9">
+      <c r="E10" s="6"/>
+      <c r="F10" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <v>257157</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9">
+      <c r="E11" s="6"/>
+      <c r="F11" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>190801</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9">
+      <c r="E12" s="6"/>
+      <c r="F12" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>273714</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9">
+      <c r="E13" s="6"/>
+      <c r="F13" s="7">
         <v>7.69</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>101728</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9">
+      <c r="E14" s="6"/>
+      <c r="F14" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>244444</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="9">
+      <c r="E15" s="6"/>
+      <c r="F15" s="7">
         <v>1.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>100876</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="9">
+      <c r="E16" s="6"/>
+      <c r="F16" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <v>106961</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="9">
+      <c r="E17" s="6"/>
+      <c r="F17" s="7">
         <v>4.49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <v>112271</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9">
+      <c r="E18" s="6"/>
+      <c r="F18" s="7">
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <v>134749</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9">
+      <c r="E19" s="6"/>
+      <c r="F19" s="7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>112978</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9">
+      <c r="E20" s="6"/>
+      <c r="F20" s="7">
         <v>2.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <v>100027</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9">
+      <c r="E21" s="6"/>
+      <c r="F21" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <v>255841</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9">
+      <c r="E22" s="6"/>
+      <c r="F22" s="7">
         <v>2.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <v>138206</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9">
+      <c r="E23" s="6"/>
+      <c r="F23" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <v>101874</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9">
+      <c r="E24" s="6"/>
+      <c r="F24" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>101083</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9">
+      <c r="E25" s="6"/>
+      <c r="F25" s="7">
         <v>7.19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>101113</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9">
+      <c r="E26" s="6"/>
+      <c r="F26" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>174382</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9">
+      <c r="E27" s="6"/>
+      <c r="F27" s="7">
         <v>38.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <v>303196</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9">
+      <c r="E28" s="6"/>
+      <c r="F28" s="7">
         <v>3.39</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <v>274807</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9">
+      <c r="E29" s="6"/>
+      <c r="F29" s="7">
         <v>2.89</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>100426</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9">
+      <c r="E31" s="6"/>
+      <c r="F31" s="7">
         <v>3.89</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="6">
+      <c r="C32" s="5">
         <v>100561</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9">
+      <c r="E32" s="6"/>
+      <c r="F32" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>100279</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9">
+      <c r="E33" s="6"/>
+      <c r="F33" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
         <v>100511</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="7">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C35" s="5">
         <v>107645</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9">
+      <c r="E35" s="6"/>
+      <c r="F35" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>228234</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9">
+      <c r="E36" s="6"/>
+      <c r="F36" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C37" s="6">
+      <c r="C37" s="5">
         <v>100373</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9">
+      <c r="E37" s="6"/>
+      <c r="F37" s="7">
         <v>26.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>236651</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9">
+      <c r="E39" s="6"/>
+      <c r="F39" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>104406</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9">
+      <c r="E41" s="6"/>
+      <c r="F41" s="7">
         <v>11.39</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="2" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="6">
+      <c r="C42" s="5">
         <v>104404</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9">
+      <c r="E42" s="6"/>
+      <c r="F42" s="7">
         <v>9.69</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="5">
         <v>104410</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9">
+      <c r="E43" s="6"/>
+      <c r="F43" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="5">
         <v>102282</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9">
+      <c r="E44" s="6"/>
+      <c r="F44" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="6">
+      <c r="C45" s="5">
         <v>286325</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9">
+      <c r="E45" s="6"/>
+      <c r="F45" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C46" s="6">
+      <c r="C46" s="5">
         <v>264452</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9">
+      <c r="E46" s="6"/>
+      <c r="F46" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C47" s="6">
+      <c r="C47" s="5">
         <v>247799</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9">
+      <c r="E47" s="6"/>
+      <c r="F47" s="7">
         <v>6.19</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="3" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C48" s="10">
+      <c r="C48" s="9">
         <v>258893</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12">
+      <c r="E48" s="8"/>
+      <c r="F48" s="10">
         <f>15*3.89</f>
         <v>58.35</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="3" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="9">
         <v>324556</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E49" s="11"/>
-      <c r="F49" s="12">
+      <c r="E49" s="8"/>
+      <c r="F49" s="10">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="6">
+      <c r="C50" s="5">
         <v>109729</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9">
+      <c r="E50" s="6"/>
+      <c r="F50" s="7">
         <v>105.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="2" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
         <v>295198</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9">
+      <c r="E51" s="6"/>
+      <c r="F51" s="7">
         <v>11.49</v>
       </c>
     </row>

--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4151CF6-51DE-465F-8DC4-4D512AACD819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A78C3AE-B3BB-41C3-B69C-5072D25A4E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -275,7 +275,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,21 +295,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -353,7 +363,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -361,28 +371,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -689,889 +703,889 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="12.28515625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="74.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>325990</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>199440</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>342706</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="8"/>
       <c r="F4" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>327443</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="8"/>
       <c r="F5" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>140665</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="8"/>
       <c r="F6" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>100054</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
       <c r="F7" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>318330</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="6"/>
+      <c r="E9" s="8"/>
       <c r="F9" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>174298</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="6"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>261728</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6"/>
+      <c r="E11" s="8"/>
       <c r="F11" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>257157</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6"/>
+      <c r="E12" s="8"/>
       <c r="F12" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>341362</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>207358</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="8"/>
       <c r="F14" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>273714</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="8"/>
       <c r="F15" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>101728</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="6"/>
+      <c r="E16" s="8"/>
       <c r="F16" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>287073</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="6"/>
+      <c r="E17" s="8"/>
       <c r="F17" s="9">
         <v>2.19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>106831</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="6"/>
+      <c r="E18" s="8"/>
       <c r="F18" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>106961</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="8" t="s">
         <v>32</v>
       </c>
       <c r="F19" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>134749</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E20" s="6"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="9">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>134629</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="6"/>
+      <c r="E21" s="8"/>
       <c r="F21" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>255841</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="6"/>
+      <c r="E22" s="8"/>
       <c r="F22" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>302126</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="6"/>
+      <c r="E23" s="8"/>
       <c r="F23" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>168910</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="6"/>
+      <c r="E24" s="8"/>
       <c r="F24" s="9">
         <v>5.19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>107118</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="6"/>
+      <c r="E25" s="8"/>
       <c r="F25" s="9">
         <v>3.69</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>155080</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="6"/>
+      <c r="E26" s="8"/>
       <c r="F26" s="9">
         <v>7.19</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>142446</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="6"/>
+      <c r="E27" s="8"/>
       <c r="F27" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>108252</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="6"/>
+      <c r="E28" s="8"/>
       <c r="F28" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>307145</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="6"/>
+      <c r="E29" s="8"/>
       <c r="F29" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>274807</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="6"/>
+      <c r="E30" s="8"/>
       <c r="F30" s="9">
         <v>2.69</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>100426</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E32" s="6"/>
+      <c r="E32" s="8"/>
       <c r="F32" s="9">
         <v>4.79</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>116139</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E33" s="6"/>
+      <c r="E33" s="8"/>
       <c r="F33" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>142863</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="6"/>
+      <c r="E34" s="8"/>
       <c r="F34" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>119826</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E35" s="6"/>
+      <c r="E35" s="8"/>
       <c r="F35" s="9">
         <v>2.79</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>170542</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E36" s="6"/>
+      <c r="E36" s="8"/>
       <c r="F36" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>261360</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E37" s="6"/>
+      <c r="E37" s="8"/>
       <c r="F37" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>261980</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="6"/>
+      <c r="E38" s="8"/>
       <c r="F38" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="6">
         <v>104406</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E40" s="6"/>
+      <c r="E40" s="8"/>
       <c r="F40" s="9">
         <v>11.49</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="6">
         <v>104410</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E41" s="6"/>
+      <c r="E41" s="8"/>
       <c r="F41" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="6">
         <v>325127</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="6"/>
+      <c r="E42" s="8"/>
       <c r="F42" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
         <v>122984</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="6"/>
+      <c r="E43" s="8"/>
       <c r="F43" s="9">
         <v>9.69</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="6">
         <v>117100</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="6"/>
+      <c r="E44" s="8"/>
       <c r="F44" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="6">
         <v>102237</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E45" s="6"/>
+      <c r="E45" s="8"/>
       <c r="F45" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="6">
         <v>264452</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E46" s="6"/>
+      <c r="E46" s="8"/>
       <c r="F46" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="6">
         <v>247799</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E47" s="6"/>
+      <c r="E47" s="8"/>
       <c r="F47" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="6">
         <v>239446</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E48" s="6"/>
+      <c r="E48" s="8"/>
       <c r="F48" s="9">
         <f>12*3.29</f>
         <v>39.480000000000004</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="6">
         <v>324556</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E49" s="6"/>
+      <c r="E49" s="8"/>
       <c r="F49" s="9">
         <f>15*2.95</f>
         <v>44.25</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="6">
         <v>109729</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E50" s="6"/>
+      <c r="E50" s="8"/>
       <c r="F50" s="9">
         <v>99.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="6">
         <v>295198</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E51" s="6"/>
+      <c r="E51" s="8"/>
       <c r="F51" s="9">
         <v>10.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
+++ b/giro_da_praça_ofertas - SEGUNDA A QUARTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7D1E8FF-7D11-4C0E-BC81-343DAF58283F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118858FF-EF48-47EC-8B9A-C57BED14C195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,21 +376,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -434,7 +444,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -442,28 +452,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,1282 +780,1289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F74"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="41.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="96.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>100020</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>22.39</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>100031</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>301961</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>116507</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>163918</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>10.19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>106680</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>345404</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6">
+      <c r="E8" s="8"/>
+      <c r="F8" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>255232</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>101137</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>114037</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>261728</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>6.59</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>257157</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>253537</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>273714</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="6">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>100785</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="6">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>188242</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>130939</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>1.89</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>100755</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6">
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>22.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>108518</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6">
+      <c r="E21" s="8"/>
+      <c r="F21" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>325476</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6">
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>109168</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6">
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>234316</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="6">
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>106854</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6">
+      <c r="E25" s="8"/>
+      <c r="F25" s="9">
         <v>12.39</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>112978</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>159684</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="6">
+      <c r="E27" s="8"/>
+      <c r="F27" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>128898</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6">
+      <c r="E28" s="8"/>
+      <c r="F28" s="9">
         <v>4.59</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>100027</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>111571</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6">
+      <c r="E30" s="8"/>
+      <c r="F30" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>100120</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="6">
+      <c r="E31" s="8"/>
+      <c r="F31" s="9">
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>157069</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="6">
+      <c r="E32" s="8"/>
+      <c r="F32" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>149122</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6">
+      <c r="E33" s="8"/>
+      <c r="F33" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>101130</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="6">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>228421</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="6">
+      <c r="E35" s="8"/>
+      <c r="F35" s="9">
         <v>44.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>101069</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="6">
+      <c r="E36" s="8"/>
+      <c r="F36" s="9">
         <v>5.69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>113183</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="6">
+      <c r="E37" s="8"/>
+      <c r="F37" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>101113</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="6">
+      <c r="E38" s="8"/>
+      <c r="F38" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="6">
         <v>174382</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="6">
+      <c r="E39" s="8"/>
+      <c r="F39" s="9">
         <v>42.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="6">
         <v>290255</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="6">
+      <c r="E40" s="8"/>
+      <c r="F40" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="6">
         <v>142475</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="6">
+      <c r="E41" s="8"/>
+      <c r="F41" s="9">
         <v>3.39</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
         <v>104406</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="6">
+      <c r="E43" s="8"/>
+      <c r="F43" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="6">
         <v>104404</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="6">
+      <c r="E44" s="8"/>
+      <c r="F44" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="6">
         <v>104416</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="6">
+      <c r="E45" s="8"/>
+      <c r="F45" s="9">
         <v>10.49</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="6">
         <v>102282</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="6">
+      <c r="E46" s="8"/>
+      <c r="F46" s="9">
         <v>8.89</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="6">
         <v>102233</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="6">
+      <c r="E47" s="8"/>
+      <c r="F47" s="9">
         <v>45.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="6">
         <v>102149</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="6">
+      <c r="E48" s="8"/>
+      <c r="F48" s="9">
         <v>6.89</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="6">
         <v>220499</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="6">
+      <c r="E49" s="8"/>
+      <c r="F49" s="9">
         <v>8.2899999999999991</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="6">
         <v>325999</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="6">
+      <c r="E50" s="8"/>
+      <c r="F50" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="6">
         <v>286362</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="6">
+      <c r="E51" s="8"/>
+      <c r="F51" s="9">
         <v>10.19</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="6">
         <v>168712</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="6">
+      <c r="E52" s="8"/>
+      <c r="F52" s="9">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="6">
         <v>136330</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="6">
+      <c r="E53" s="8"/>
+      <c r="F53" s="9">
         <f>12*4.19</f>
         <v>50.28</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="6">
         <v>102085</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="6">
+      <c r="E54" s="8"/>
+      <c r="F54" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="6">
         <v>109726</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="6">
+      <c r="E55" s="8"/>
+      <c r="F55" s="9">
         <v>249.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="6">
         <v>257145</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="6">
+      <c r="E57" s="8"/>
+      <c r="F57" s="9">
         <v>2.69</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="6">
         <v>100426</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="6">
+      <c r="E58" s="8"/>
+      <c r="F58" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="6">
         <v>116139</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="6">
+      <c r="E59" s="8"/>
+      <c r="F59" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="6">
         <v>157034</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="6">
+      <c r="E60" s="8"/>
+      <c r="F60" s="9">
         <v>25.99</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="6">
         <v>193904</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="6">
+      <c r="E61" s="8"/>
+      <c r="F61" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="6">
         <v>100391</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="6">
+      <c r="E62" s="8"/>
+      <c r="F62" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="6">
         <v>100511</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="6">
+      <c r="E63" s="8"/>
+      <c r="F63" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="6">
         <v>155830</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="6">
+      <c r="E64" s="8"/>
+      <c r="F64" s="9">
         <v>9.19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="6">
         <v>107645</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="6">
+      <c r="E65" s="8"/>
+      <c r="F65" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="6">
         <v>257710</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="6">
+      <c r="E66" s="8"/>
+      <c r="F66" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="6">
         <v>261980</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="6">
+      <c r="E67" s="8"/>
+      <c r="F67" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="6">
         <v>261083</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="6">
+      <c r="E68" s="8"/>
+      <c r="F68" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="6">
         <v>100373</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="6">
+      <c r="E69" s="8"/>
+      <c r="F69" s="9">
         <v>25.99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="6">
         <v>103682</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="6">
+      <c r="E71" s="8"/>
+      <c r="F71" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="6">
         <v>292044</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="6">
+      <c r="E72" s="8"/>
+      <c r="F72" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="6">
         <v>108140</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="6">
+      <c r="E73" s="8"/>
+      <c r="F73" s="9">
         <v>4.79</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="6">
         <v>346964</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="6">
+      <c r="E74" s="8"/>
+      <c r="F74" s="9">
         <v>13.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>